--- a/output/2026年4月/党费收缴子表/2026年4月-中共新疆大学计算机科学与技术学院研究生第五支部委员会-党费收缴子表.xlsx
+++ b/output/2026年4月/党费收缴子表/2026年4月-中共新疆大学计算机科学与技术学院研究生第五支部委员会-党费收缴子表.xlsx
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0</v>
+        <v>1370</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0</v>
@@ -620,10 +620,10 @@
         <v>0</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0</v>
+        <v>1370</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0</v>
+        <v>1371</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>0</v>
@@ -669,10 +669,10 @@
         <v>0</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0</v>
+        <v>1371</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="6">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0</v>
+        <v>1372</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>0</v>
@@ -718,10 +718,10 @@
         <v>0</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0</v>
+        <v>1372</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="7">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0</v>
+        <v>1373</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>0</v>
@@ -767,10 +767,10 @@
         <v>0</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0</v>
+        <v>1373</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="8">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0</v>
+        <v>1374</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>0</v>
@@ -816,10 +816,10 @@
         <v>0</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0</v>
+        <v>1374</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="9">
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0</v>
+        <v>1375</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>0</v>
@@ -865,10 +865,10 @@
         <v>0</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0</v>
+        <v>1375</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="10">
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0</v>
+        <v>1376</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>0</v>
@@ -914,10 +914,10 @@
         <v>0</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0</v>
+        <v>1376</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>0</v>
+        <v>1377</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>0</v>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0</v>
+        <v>1377</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="12">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0</v>
+        <v>1378</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>0</v>
@@ -1012,10 +1012,10 @@
         <v>0</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0</v>
+        <v>1378</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="13">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>0</v>
+        <v>1379</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0</v>
+        <v>1379</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="14">
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0</v>
+        <v>1380</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>0</v>
@@ -1110,10 +1110,10 @@
         <v>0</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0</v>
+        <v>1380</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="15">
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0</v>
+        <v>1381</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>0</v>
@@ -1159,10 +1159,10 @@
         <v>0</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0</v>
+        <v>1381</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="16">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0</v>
+        <v>1382</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>0</v>
@@ -1208,10 +1208,10 @@
         <v>0</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0</v>
+        <v>1382</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="17">
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0</v>
+        <v>1383</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>0</v>
@@ -1257,10 +1257,10 @@
         <v>0</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0</v>
+        <v>1383</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="18">
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>0</v>
@@ -1306,10 +1306,10 @@
         <v>0</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="19">
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0</v>
+        <v>1385</v>
       </c>
       <c r="D19" s="6" t="n">
         <v>0</v>
@@ -1355,10 +1355,10 @@
         <v>0</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0</v>
+        <v>1385</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="20">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0</v>
+        <v>1386</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>0</v>
@@ -1404,10 +1404,10 @@
         <v>0</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0</v>
+        <v>1386</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="21">
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>0</v>
+        <v>1387</v>
       </c>
       <c r="D21" s="6" t="n">
         <v>0</v>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0</v>
+        <v>1387</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="22">
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0</v>
+        <v>1388</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>0</v>
@@ -1502,10 +1502,10 @@
         <v>0</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0</v>
+        <v>1388</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="23">
@@ -1518,7 +1518,7 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>0</v>
+        <v>1389</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>0</v>
@@ -1551,10 +1551,10 @@
         <v>0</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0</v>
+        <v>1389</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="24">
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0</v>
+        <v>1390</v>
       </c>
       <c r="D24" s="4" t="n">
         <v>0</v>
@@ -1600,10 +1600,10 @@
         <v>0</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0</v>
+        <v>1390</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>0</v>
+        <v>1391</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0</v>
+        <v>1391</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0</v>
+        <v>1392</v>
       </c>
       <c r="D26" s="4" t="n">
         <v>0</v>
@@ -1698,10 +1698,10 @@
         <v>0</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0</v>
+        <v>1392</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>0</v>
+        <v>1393</v>
       </c>
       <c r="D27" s="6" t="n">
         <v>0</v>
@@ -1747,10 +1747,10 @@
         <v>0</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0</v>
+        <v>1393</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0</v>
+        <v>1394</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>0</v>
@@ -1796,10 +1796,10 @@
         <v>0</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0</v>
+        <v>1394</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>0</v>
+        <v>1395</v>
       </c>
       <c r="D29" s="6" t="n">
         <v>0</v>
@@ -1845,10 +1845,10 @@
         <v>0</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0</v>
+        <v>1395</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0</v>
+        <v>1396</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0</v>
+        <v>1396</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>0</v>
+        <v>1397</v>
       </c>
       <c r="D31" s="6" t="n">
         <v>0</v>
@@ -1943,10 +1943,10 @@
         <v>0</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0</v>
+        <v>1397</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0</v>
+        <v>1398</v>
       </c>
       <c r="D32" s="4" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0</v>
+        <v>1398</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>0</v>
+        <v>1399</v>
       </c>
       <c r="D33" s="6" t="n">
         <v>0</v>
@@ -2041,10 +2041,10 @@
         <v>0</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0</v>
+        <v>1399</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>0</v>
@@ -2090,10 +2090,10 @@
         <v>0</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0</v>
+        <v>1401</v>
       </c>
       <c r="D35" s="6" t="n">
         <v>0</v>
@@ -2139,10 +2139,10 @@
         <v>0</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0</v>
+        <v>1401</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0</v>
+        <v>1402</v>
       </c>
       <c r="D36" s="4" t="n">
         <v>0</v>
@@ -2188,10 +2188,10 @@
         <v>0</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0</v>
+        <v>1402</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0</v>
+        <v>1403</v>
       </c>
       <c r="D37" s="6" t="n">
         <v>0</v>
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0</v>
+        <v>1403</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>0</v>
+        <v>1404</v>
       </c>
       <c r="D38" s="4" t="n">
         <v>0</v>
@@ -2286,10 +2286,10 @@
         <v>0</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0</v>
+        <v>1404</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>0</v>
+        <v>1405</v>
       </c>
       <c r="D39" s="6" t="n">
         <v>0</v>
@@ -2335,10 +2335,10 @@
         <v>0</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0</v>
+        <v>1405</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40">
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>0</v>
+        <v>1406</v>
       </c>
       <c r="D40" s="4" t="n">
         <v>0</v>
@@ -2384,10 +2384,10 @@
         <v>0</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0</v>
+        <v>1406</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="C41" s="6" t="n">
-        <v>0</v>
+        <v>1407</v>
       </c>
       <c r="D41" s="6" t="n">
         <v>0</v>
@@ -2433,10 +2433,10 @@
         <v>0</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0</v>
+        <v>1407</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>0</v>
+        <v>1408</v>
       </c>
       <c r="D42" s="4" t="n">
         <v>0</v>
@@ -2482,10 +2482,10 @@
         <v>0</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0</v>
+        <v>1408</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>0</v>
+        <v>1409</v>
       </c>
       <c r="D43" s="6" t="n">
         <v>0</v>
@@ -2531,10 +2531,10 @@
         <v>0</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0</v>
+        <v>1409</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>0</v>
+        <v>1410</v>
       </c>
       <c r="D44" s="4" t="n">
         <v>0</v>
@@ -2580,10 +2580,10 @@
         <v>0</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>0</v>
+        <v>1410</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>0</v>
+        <v>1411</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>0</v>
@@ -2629,10 +2629,10 @@
         <v>0</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0</v>
+        <v>1411</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="46">
@@ -2645,7 +2645,7 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0</v>
+        <v>1412</v>
       </c>
       <c r="D46" s="4" t="n">
         <v>0</v>
@@ -2678,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0</v>
+        <v>1412</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="47">
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="C47" s="6" t="n">
-        <v>0</v>
+        <v>1413</v>
       </c>
       <c r="D47" s="6" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0</v>
+        <v>1413</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="48">
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0</v>
+        <v>1414</v>
       </c>
       <c r="D48" s="4" t="n">
         <v>0</v>
@@ -2776,10 +2776,10 @@
         <v>0</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0</v>
+        <v>1414</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="49">
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C49" s="6" t="n">
-        <v>0</v>
+        <v>1415</v>
       </c>
       <c r="D49" s="6" t="n">
         <v>0</v>
@@ -2825,10 +2825,10 @@
         <v>0</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0</v>
+        <v>1415</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="50">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>0</v>
+        <v>1416</v>
       </c>
       <c r="D50" s="4" t="n">
         <v>0</v>
@@ -2874,10 +2874,10 @@
         <v>0</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0</v>
+        <v>1416</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="51">
@@ -2900,7 +2900,7 @@
       <c r="M51" s="8" t="n"/>
       <c r="N51" s="8" t="n"/>
       <c r="O51" s="3" t="n">
-        <v>0</v>
+        <v>327.6000000000002</v>
       </c>
     </row>
   </sheetData>
